--- a/dataDefinitions.xlsx
+++ b/dataDefinitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\workspaces\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\workspaces\SchroederLab\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4430D0-E227-4164-8957-C66690F8EE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4347F496-96DE-4FBF-B86D-C16A8C3DF4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1958" yWindow="-16297" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{3F3756E1-F16D-4C67-A02C-119F78A23B8F}"/>
+    <workbookView xWindow="30623" yWindow="-98" windowWidth="30915" windowHeight="16755" activeTab="3" xr2:uid="{3F3756E1-F16D-4C67-A02C-119F78A23B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Imaging" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="StimRespFits" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="357">
   <si>
     <t>File name</t>
   </si>
@@ -921,9 +922,6 @@
     <t>number of grids from top to bottom, number of grids from left to right, and bottom, top , left, right,edge of each stimulus frame relative to visual field. 0 -&gt; horizon/midline</t>
   </si>
   <si>
-    <t>natual.startTime.npy</t>
-  </si>
-  <si>
     <t>natural.endTime.npy</t>
   </si>
   <si>
@@ -1093,13 +1091,34 @@
   </si>
   <si>
     <t>recording.scChannels</t>
+  </si>
+  <si>
+    <t>(left, right, top, bottom) edge of each stimulus frame relative to visual field. 0 -&gt; horizon/midline; postive values for top/bottom -&gt; above horizon</t>
+  </si>
+  <si>
+    <t>double [-1,0,1]</t>
+  </si>
+  <si>
+    <t>value for each square -1 to 1 (-1 black , 0 gray, 1 white)</t>
+  </si>
+  <si>
+    <t>luminance.times</t>
+  </si>
+  <si>
+    <t>luminance.value</t>
+  </si>
+  <si>
+    <t>luminanceExp.intervals</t>
+  </si>
+  <si>
+    <t>natural.startTime.npy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1146,6 +1165,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1217,7 +1250,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1258,6 +1291,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1576,16 +1621,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C25F9AC-6BF1-4115-A50A-42D1CDBFF915}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.46484375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.86328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="157.46484375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.1328125" style="1"/>
+    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="157.42578125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1599,7 +1644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
@@ -1613,7 +1658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>17</v>
       </c>
@@ -1627,11 +1672,11 @@
         <v>226</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>22</v>
       </c>
@@ -1645,7 +1690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>283</v>
       </c>
@@ -1659,7 +1704,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1673,7 +1718,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>19</v>
       </c>
@@ -1687,7 +1732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1701,7 +1746,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>20</v>
       </c>
@@ -1715,7 +1760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>21</v>
       </c>
@@ -1729,7 +1774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>290</v>
       </c>
@@ -1743,7 +1788,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>179</v>
       </c>
@@ -1757,7 +1802,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>205</v>
       </c>
@@ -1771,9 +1816,9 @@
         <v>228</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>117</v>
@@ -1782,12 +1827,12 @@
         <v>8</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>117</v>
@@ -1796,12 +1841,12 @@
         <v>8</v>
       </c>
       <c r="D18" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>306</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>117</v>
@@ -1810,12 +1855,12 @@
         <v>8</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>117</v>
@@ -1824,12 +1869,12 @@
         <v>8</v>
       </c>
       <c r="D20" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>310</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>117</v>
@@ -1838,12 +1883,12 @@
         <v>8</v>
       </c>
       <c r="D21" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>312</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>117</v>
@@ -1852,23 +1897,23 @@
         <v>8</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D23" s="10"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -1882,7 +1927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -1902,16 +1947,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB1A0A7-F272-47D7-84D8-7D69F6A764BE}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.46484375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.86328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="157.46484375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.1328125" style="1"/>
+    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="157.42578125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1925,7 +1970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
@@ -1939,7 +1984,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -1953,7 +1998,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>101</v>
       </c>
@@ -1967,7 +2012,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>106</v>
       </c>
@@ -1981,7 +2026,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
@@ -1995,7 +2040,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -2009,7 +2054,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>113</v>
       </c>
@@ -2023,13 +2068,13 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
@@ -2043,7 +2088,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -2057,7 +2102,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
@@ -2071,7 +2116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -2085,7 +2130,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>54</v>
       </c>
@@ -2099,10 +2144,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -2116,7 +2161,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
@@ -2130,7 +2175,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
@@ -2144,7 +2189,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,7 +2203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
@@ -2172,7 +2217,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -2186,7 +2231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -2200,7 +2245,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>77</v>
       </c>
@@ -2214,7 +2259,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
@@ -2228,7 +2273,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>45</v>
       </c>
@@ -2242,7 +2287,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>70</v>
       </c>
@@ -2256,7 +2301,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>46</v>
       </c>
@@ -2270,7 +2315,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -2284,18 +2329,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -2307,16 +2352,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBC7223-8FD1-49F7-AA31-6BD218EA8AEE}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.46484375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.86328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="157.46484375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.1328125" style="1"/>
+    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="157.42578125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2330,7 +2375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
@@ -2344,7 +2389,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>272</v>
       </c>
@@ -2358,11 +2403,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>80</v>
       </c>
@@ -2376,7 +2421,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>81</v>
       </c>
@@ -2390,7 +2435,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>274</v>
       </c>
@@ -2404,7 +2449,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>240</v>
       </c>
@@ -2418,11 +2463,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>286</v>
       </c>
@@ -2436,7 +2481,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>288</v>
       </c>
@@ -2450,7 +2495,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>273</v>
       </c>
@@ -2471,17 +2516,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F47D32-613F-478F-B67D-600975316B20}">
-  <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D64"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.86328125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="16.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="110.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="157.46484375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="28.85546875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="16.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="110.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="157.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2495,7 +2540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>201</v>
       </c>
@@ -2509,7 +2554,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>202</v>
       </c>
@@ -2523,7 +2568,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>213</v>
       </c>
@@ -2537,7 +2582,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>183</v>
       </c>
@@ -2551,7 +2596,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>184</v>
       </c>
@@ -2565,7 +2610,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>185</v>
       </c>
@@ -2579,7 +2624,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>278</v>
       </c>
@@ -2593,49 +2638,38 @@
         <v>279</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>214</v>
       </c>
@@ -2643,379 +2677,371 @@
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="15"/>
+    </row>
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B19" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C19" s="18">
+        <v>4</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="16">
         <v>6</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D20" s="15" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="5" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B35" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C36" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" s="1" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D43" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
@@ -3027,9 +3053,9 @@
         <v>218</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>6</v>
@@ -3041,9 +3067,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
@@ -3055,37 +3081,23 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>296</v>
+        <v>189</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A51" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
@@ -3097,24 +3109,110 @@
         <v>218</v>
       </c>
     </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAE84D7-1D35-455E-9EAE-38426D5ED717}">
   <dimension ref="A1:D69"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.86328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="157.46484375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.1328125" style="1"/>
+    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="157.42578125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3128,7 +3226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>116</v>
       </c>
@@ -3142,7 +3240,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>119</v>
       </c>
@@ -3156,13 +3254,13 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>132</v>
       </c>
@@ -3176,7 +3274,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>133</v>
       </c>
@@ -3190,7 +3288,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>134</v>
       </c>
@@ -3204,7 +3302,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>135</v>
       </c>
@@ -3218,7 +3316,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>136</v>
       </c>
@@ -3232,7 +3330,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>137</v>
       </c>
@@ -3246,13 +3344,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>138</v>
       </c>
@@ -3266,7 +3364,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>139</v>
       </c>
@@ -3278,7 +3376,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>140</v>
       </c>
@@ -3290,7 +3388,7 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>141</v>
       </c>
@@ -3302,7 +3400,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>142</v>
       </c>
@@ -3313,7 +3411,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>143</v>
       </c>
@@ -3325,7 +3423,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>144</v>
       </c>
@@ -3339,7 +3437,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>145</v>
       </c>
@@ -3350,7 +3448,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>146</v>
       </c>
@@ -3361,7 +3459,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>147</v>
       </c>
@@ -3372,7 +3470,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
@@ -3383,7 +3481,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -3394,7 +3492,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>150</v>
       </c>
@@ -3408,7 +3506,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>151</v>
       </c>
@@ -3419,7 +3517,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>152</v>
       </c>
@@ -3430,7 +3528,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>153</v>
       </c>
@@ -3441,7 +3539,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>154</v>
       </c>
@@ -3452,7 +3550,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>155</v>
       </c>
@@ -3464,7 +3562,7 @@
       </c>
       <c r="D31" s="5"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>129</v>
       </c>
@@ -3478,7 +3576,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>130</v>
       </c>
@@ -3492,7 +3590,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>131</v>
       </c>
@@ -3506,7 +3604,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>258</v>
       </c>
@@ -3520,7 +3618,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>160</v>
       </c>
@@ -3534,7 +3632,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>161</v>
       </c>
@@ -3548,7 +3646,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>163</v>
       </c>
@@ -3562,7 +3660,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>162</v>
       </c>
@@ -3576,7 +3674,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>164</v>
       </c>
@@ -3590,7 +3688,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>264</v>
       </c>
@@ -3604,7 +3702,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>265</v>
       </c>
@@ -3618,7 +3716,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>156</v>
       </c>
@@ -3632,7 +3730,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>177</v>
       </c>
@@ -3646,7 +3744,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>200</v>
       </c>
@@ -3660,7 +3758,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>157</v>
       </c>
@@ -3674,7 +3772,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>158</v>
       </c>
@@ -3688,7 +3786,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>159</v>
       </c>
@@ -3702,7 +3800,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>266</v>
       </c>
@@ -3716,7 +3814,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>271</v>
       </c>
@@ -3730,177 +3828,177 @@
         <v>270</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B57" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="14" t="s">
+      <c r="D57" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="D57" s="14" t="s">
+    </row>
+    <row r="58" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A58" s="1" t="s">
+      <c r="B58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D58" s="1" t="s">
+    </row>
+    <row r="59" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A59" s="1" t="s">
+      <c r="B59" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D59" s="1" t="s">
+    </row>
+    <row r="60" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A60" s="1" t="s">
+      <c r="B60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D60" s="1" t="s">
+    </row>
+    <row r="61" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A61" s="1" t="s">
+      <c r="B61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D61" s="1" t="s">
+    </row>
+    <row r="62" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A62" s="1" t="s">
+      <c r="B62" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D62" s="1" t="s">
+    </row>
+    <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A63" s="1" t="s">
+      <c r="B63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D63" s="1" t="s">
+    </row>
+    <row r="64" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" s="1" t="s">
+      <c r="B64" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D64" s="1" t="s">
+    </row>
+    <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A65" s="1" t="s">
+      <c r="B65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D65" s="1" t="s">
+    </row>
+    <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A66" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D66" s="1" t="s">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="1" t="s">
+      <c r="B68" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>117</v>
@@ -3909,7 +4007,7 @@
         <v>91</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/dataDefinitions.xlsx
+++ b/dataDefinitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\workspaces\SchroederLab\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4347F496-96DE-4FBF-B86D-C16A8C3DF4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6981018-D531-4A84-9E98-5608BEB5395D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30623" yWindow="-98" windowWidth="30915" windowHeight="16755" activeTab="3" xr2:uid="{3F3756E1-F16D-4C67-A02C-119F78A23B8F}"/>
+    <workbookView xWindow="5340" yWindow="915" windowWidth="21600" windowHeight="13275" activeTab="3" xr2:uid="{3F3756E1-F16D-4C67-A02C-119F78A23B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Imaging" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="StimRespFits" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -883,15 +882,9 @@
     <t>whether of not the grating was rewarded</t>
   </si>
   <si>
-    <t>gratingsExp.description</t>
-  </si>
-  <si>
     <t>nSession,1</t>
   </si>
   <si>
-    <t>the description of the grating session (grating - for normal presentation, or oddball for oddball sessions)</t>
-  </si>
-  <si>
     <t>planes.zcorrelation</t>
   </si>
   <si>
@@ -1112,6 +1105,12 @@
   </si>
   <si>
     <t>natural.startTime.npy</t>
+  </si>
+  <si>
+    <t>gratingsExp.description.csv</t>
+  </si>
+  <si>
+    <t>the description of the grating session (grating type, atropine or not)</t>
   </si>
 </sst>
 </file>
@@ -1692,16 +1691,16 @@
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1776,7 +1775,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>197</v>
@@ -1785,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,7 +1817,7 @@
     </row>
     <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>117</v>
@@ -1827,12 +1826,12 @@
         <v>8</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>117</v>
@@ -1841,12 +1840,12 @@
         <v>8</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>117</v>
@@ -1855,12 +1854,12 @@
         <v>8</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>117</v>
@@ -1869,12 +1868,12 @@
         <v>8</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>117</v>
@@ -1883,12 +1882,12 @@
         <v>8</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>117</v>
@@ -1897,7 +1896,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2331,16 +2330,16 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2469,7 +2468,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -2478,12 +2477,12 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -2492,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,16 +2642,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>280</v>
+        <v>355</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>282</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2702,13 +2701,13 @@
         <v>186</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>91</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2742,7 +2741,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2756,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3111,7 +3110,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>6</v>
@@ -3125,7 +3124,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>6</v>
@@ -3139,35 +3138,35 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>6</v>
@@ -3181,17 +3180,17 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -3830,175 +3829,175 @@
     </row>
     <row r="57" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>314</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>117</v>
@@ -4007,7 +4006,7 @@
         <v>91</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
